--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,39 +1221,39 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>power_restored</t>
+          <t>unreachable</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>notify.type.power_restored.name</t>
+          <t>notify.type.unreachable.name</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>notify.type.power_restored.single</t>
+          <t>notify.type.unreachable.single</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>notify.type.power_restored.many</t>
+          <t>notify.type.unreachable.many</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PowerRestored</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -1266,7 +1266,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>signal_restored</t>
+          <t>power_restored</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1276,22 +1276,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>notify.type.signal_restored.name</t>
+          <t>notify.type.power_restored.name</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>notify.type.signal_restored.single</t>
+          <t>notify.type.power_restored.single</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>notify.type.signal_restored.many</t>
+          <t>notify.type.power_restored.many</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SignalRestored</t>
+          <t>PowerRestored</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1311,7 +1311,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>production_complete</t>
+          <t>signal_restored</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1321,29 +1321,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>notify.type.production_complete.name</t>
+          <t>notify.type.signal_restored.name</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>notify.type.production_complete.single</t>
+          <t>notify.type.signal_restored.single</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>notify.type.production_complete.many</t>
+          <t>notify.type.signal_restored.many</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ProductionComplete</t>
+          <t>SignalRestored</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -1356,7 +1356,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>analysis_complete</t>
+          <t>production_complete</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1366,22 +1366,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>notify.type.analysis_complete.name</t>
+          <t>notify.type.production_complete.name</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>notify.type.analysis_complete.single</t>
+          <t>notify.type.production_complete.single</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>notify.type.analysis_complete.many</t>
+          <t>notify.type.production_complete.many</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AnalysisComplete</t>
+          <t>ProductionComplete</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1401,7 +1401,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>build_complete</t>
+          <t>analysis_complete</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1411,22 +1411,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>notify.type.build_complete.name</t>
+          <t>notify.type.analysis_complete.name</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>notify.type.build_complete.single</t>
+          <t>notify.type.analysis_complete.single</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>notify.type.build_complete.many</t>
+          <t>notify.type.analysis_complete.many</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BuildComplete</t>
+          <t>AnalysisComplete</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1446,7 +1446,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>objective_new</t>
+          <t>build_complete</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1456,29 +1456,29 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>notify.type.objective_new.name</t>
+          <t>notify.type.build_complete.name</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>notify.type.objective_new.single</t>
+          <t>notify.type.build_complete.single</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>notify.type.objective_new.many</t>
+          <t>notify.type.build_complete.many</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ObjectiveActivated</t>
+          <t>BuildComplete</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -1491,7 +1491,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>objective_done</t>
+          <t>objective_new</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1501,22 +1501,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>notify.type.objective_done.name</t>
+          <t>notify.type.objective_new.name</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>notify.type.objective_done.single</t>
+          <t>notify.type.objective_new.single</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>notify.type.objective_done.many</t>
+          <t>notify.type.objective_new.many</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ObjectiveComplete</t>
+          <t>ObjectiveActivated</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1536,7 +1536,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>expedition</t>
+          <t>objective_done</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>notify.type.expedition.name</t>
+          <t>notify.type.objective_done.name</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>notify.type.expedition.single</t>
+          <t>notify.type.objective_done.single</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>notify.type.expedition.many</t>
+          <t>notify.type.objective_done.many</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ExpeditionDepart|Evacuate</t>
+          <t>ObjectiveComplete</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1581,7 +1581,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boss_destroyed</t>
+          <t>expedition</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1591,22 +1591,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>notify.type.boss_destroyed.name</t>
+          <t>notify.type.expedition.name</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>notify.type.boss_destroyed.single</t>
+          <t>notify.type.expedition.single</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>notify.type.boss_destroyed.many</t>
+          <t>notify.type.expedition.many</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BossDestroyed</t>
+          <t>ExpeditionDepart|Evacuate</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1626,7 +1626,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>beacon</t>
+          <t>boss_destroyed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1636,22 +1636,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>notify.type.beacon.name</t>
+          <t>notify.type.boss_destroyed.name</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>notify.type.beacon.single</t>
+          <t>notify.type.boss_destroyed.single</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>notify.type.beacon.many</t>
+          <t>notify.type.boss_destroyed.many</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BeaconLaunch|Victory</t>
+          <t>BossDestroyed</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1671,7 +1671,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>research_done</t>
+          <t>beacon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1681,29 +1681,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>notify.type.research_done.name</t>
+          <t>notify.type.beacon.name</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>notify.type.research_done.single</t>
+          <t>notify.type.beacon.single</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>notify.type.research_done.many</t>
+          <t>notify.type.beacon.many</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>BeaconLaunch|Victory</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -1716,7 +1716,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>auto_paused</t>
+          <t>research_done</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1726,17 +1726,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>notify.type.auto_paused.name</t>
+          <t>notify.type.research_done.name</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>notify.type.auto_paused.single</t>
+          <t>notify.type.research_done.single</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>notify.type.auto_paused.many</t>
+          <t>notify.type.research_done.many</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -1761,7 +1761,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>settings_changed</t>
+          <t>auto_paused</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>notify.type.settings_changed.name</t>
+          <t>notify.type.auto_paused.name</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>notify.type.settings_changed.single</t>
+          <t>notify.type.auto_paused.single</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>notify.type.settings_changed.many</t>
+          <t>notify.type.auto_paused.many</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1806,7 +1806,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>feature_locked</t>
+          <t>settings_changed</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.name</t>
+          <t>notify.type.settings_changed.name</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.single</t>
+          <t>notify.type.settings_changed.single</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.many</t>
+          <t>notify.type.settings_changed.many</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1841,10 +1841,55 @@
         <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>280</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>feature_locked</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.name</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.single</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.many</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1851,27 +1851,27 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>feature_locked</t>
+          <t>signal_coverage_left</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.name</t>
+          <t>notify.type.signal_coverage_left.name</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.single</t>
+          <t>notify.type.signal_coverage_left.single</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.many</t>
+          <t>notify.type.signal_coverage_left.many</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1883,13 +1883,148 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>290</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>signal_coverage_back</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>notify.type.signal_coverage_back.name</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>notify.type.signal_coverage_back.single</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>notify.type.signal_coverage_back.many</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>signal_relay_cut</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>notify.type.signal_relay_cut.name</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>notify.type.signal_relay_cut.single</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>notify.type.signal_relay_cut.many</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>feature_locked</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.name</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.single</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.many</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1986,27 +1986,27 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>feature_locked</t>
+          <t>construction_waiting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.name</t>
+          <t>notify.type.construction_waiting.name</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.single</t>
+          <t>notify.type.construction_waiting.single</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.many</t>
+          <t>notify.type.construction_waiting.many</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2018,13 +2018,103 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>320</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>construction_no_labor</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>notify.type.construction_no_labor.name</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>notify.type.construction_no_labor.single</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>notify.type.construction_no_labor.many</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>feature_locked</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.name</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.single</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.many</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2076,27 +2076,27 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>feature_locked</t>
+          <t>power_split</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.name</t>
+          <t>notify.type.power_split.name</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.single</t>
+          <t>notify.type.power_split.single</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.many</t>
+          <t>notify.type.power_split.many</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2108,13 +2108,103 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>340</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>power_unconnected</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>notify.type.power_unconnected.name</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>notify.type.power_unconnected.single</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>notify.type.power_unconnected.many</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>feature_locked</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.name</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.single</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.many</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2166,7 +2166,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>feature_locked</t>
+          <t>plan_undo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.name</t>
+          <t>notify.type.plan_undo.name</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.single</t>
+          <t>notify.type.plan_undo.single</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.many</t>
+          <t>notify.type.plan_undo.many</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2198,13 +2198,58 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>360</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>feature_locked</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.name</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.single</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.many</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>370</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,6 +2252,51 @@
         <v>370</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>overlay_home_only</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>notify.type.overlay_home_only.name</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>notify.type.overlay_home_only.single</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>notify.type.overlay_home_only.many</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>380</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2297,6 +2297,96 @@
         <v>380</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>power_fuel_out</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>notify.type.power_fuel_out.name</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>notify.type.power_fuel_out.single</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>notify.type.power_fuel_out.many</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>power_storage_empty</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>notify.type.power_storage_empty.name</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>notify.type.power_storage_empty.single</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>notify.type.power_storage_empty.many</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2387,6 +2387,96 @@
         <v>400</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>building_damaged</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>notify.type.building_damaged.name</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>notify.type.building_damaged.single</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>notify.type.building_damaged.many</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>building_destroyed</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>urgent</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>notify.type.building_destroyed.name</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>notify.type.building_destroyed.single</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>notify.type.building_destroyed.many</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>420</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2477,6 +2477,51 @@
         <v>420</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>standing_rule</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>notify.type.standing_rule.name</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>notify.type.standing_rule.single</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>notify.type.standing_rule.many</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>430</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2522,6 +2522,51 @@
         <v>430</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>eco_deficit</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>notify.type.eco_deficit.name</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>notify.type.eco_deficit.single</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>notify.type.eco_deficit.many</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>440</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,11 @@
           <t>sortOrder</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>awaySection</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +534,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -584,6 +594,11 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>筛选下拉里的排序</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>FG4-ECO-09:离家期间发生时记进离家报告的哪一段(production/bottleneck/power/weather/machines/raid/event/research/buildings;none=不记);对照在 fgdata_away.py</t>
         </is>
       </c>
     </row>
@@ -631,6 +646,11 @@
       <c r="K4" t="n">
         <v>10</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -676,6 +696,11 @@
       <c r="K5" t="n">
         <v>20</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -721,6 +746,11 @@
       <c r="K6" t="n">
         <v>30</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -766,6 +796,11 @@
       <c r="K7" t="n">
         <v>40</v>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -811,6 +846,11 @@
       <c r="K8" t="n">
         <v>50</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -856,6 +896,11 @@
       <c r="K9" t="n">
         <v>60</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -901,6 +946,11 @@
       <c r="K10" t="n">
         <v>70</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>raid</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -946,6 +996,11 @@
       <c r="K11" t="n">
         <v>80</v>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -991,6 +1046,11 @@
       <c r="K12" t="n">
         <v>90</v>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1036,6 +1096,11 @@
       <c r="K13" t="n">
         <v>100</v>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1081,6 +1146,11 @@
       <c r="K14" t="n">
         <v>110</v>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1126,6 +1196,11 @@
       <c r="K15" t="n">
         <v>120</v>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>machines</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1171,6 +1246,11 @@
       <c r="K16" t="n">
         <v>130</v>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1216,6 +1296,11 @@
       <c r="K17" t="n">
         <v>140</v>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1261,6 +1346,11 @@
       <c r="K18" t="n">
         <v>150</v>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1306,6 +1396,11 @@
       <c r="K19" t="n">
         <v>160</v>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1351,6 +1446,11 @@
       <c r="K20" t="n">
         <v>170</v>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1396,6 +1496,11 @@
       <c r="K21" t="n">
         <v>180</v>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1441,6 +1546,11 @@
       <c r="K22" t="n">
         <v>190</v>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1486,6 +1596,11 @@
       <c r="K23" t="n">
         <v>200</v>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1531,6 +1646,11 @@
       <c r="K24" t="n">
         <v>210</v>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1576,6 +1696,11 @@
       <c r="K25" t="n">
         <v>220</v>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1621,6 +1746,11 @@
       <c r="K26" t="n">
         <v>230</v>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1666,6 +1796,11 @@
       <c r="K27" t="n">
         <v>240</v>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1711,6 +1846,11 @@
       <c r="K28" t="n">
         <v>250</v>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -1756,6 +1896,11 @@
       <c r="K29" t="n">
         <v>260</v>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -1801,6 +1946,11 @@
       <c r="K30" t="n">
         <v>270</v>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -1846,6 +1996,11 @@
       <c r="K31" t="n">
         <v>280</v>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -1891,6 +2046,11 @@
       <c r="K32" t="n">
         <v>290</v>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -1936,6 +2096,11 @@
       <c r="K33" t="n">
         <v>300</v>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -1981,6 +2146,11 @@
       <c r="K34" t="n">
         <v>310</v>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -2026,6 +2196,11 @@
       <c r="K35" t="n">
         <v>320</v>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -2071,6 +2246,11 @@
       <c r="K36" t="n">
         <v>330</v>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -2116,6 +2296,11 @@
       <c r="K37" t="n">
         <v>340</v>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -2161,6 +2346,11 @@
       <c r="K38" t="n">
         <v>350</v>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -2206,6 +2396,11 @@
       <c r="K39" t="n">
         <v>360</v>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -2251,6 +2446,11 @@
       <c r="K40" t="n">
         <v>370</v>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -2296,6 +2496,11 @@
       <c r="K41" t="n">
         <v>380</v>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -2341,6 +2546,11 @@
       <c r="K42" t="n">
         <v>390</v>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -2386,6 +2596,11 @@
       <c r="K43" t="n">
         <v>400</v>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -2431,6 +2646,11 @@
       <c r="K44" t="n">
         <v>410</v>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -2476,6 +2696,11 @@
       <c r="K45" t="n">
         <v>420</v>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -2521,6 +2746,11 @@
       <c r="K46" t="n">
         <v>430</v>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -2565,6 +2795,261 @@
       </c>
       <c r="K47" t="n">
         <v>440</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>input_starved</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>notify.type.input_starved.name</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>notify.type.input_starved.single</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>notify.type.input_starved.many</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>10</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>450</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>output_blocked</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>notify.type.output_blocked.name</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>notify.type.output_blocked.single</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>notify.type.output_blocked.many</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>460</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>bottleneck</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>machine_wounded</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>notify.type.machine_wounded.name</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>notify.type.machine_wounded.single</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>notify.type.machine_wounded.many</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>470</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>world_event</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>notify.type.world_event.name</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>notify.type.world_event.single</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>notify.type.world_event.many</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>8</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>480</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>away_report</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>notify.type.away_report.name</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>notify.type.away_report.single</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>notify.type.away_report.many</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>490</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EmergencyRescue</t>
+          <t>EmergencyRescue|EmergencyPrint</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -3049,6 +3049,156 @@
       <c r="L52" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>core_emergency_scrap</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>notify.type.core_emergency_scrap.name</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>notify.type.core_emergency_scrap.single</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>notify.type.core_emergency_scrap.many</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>500</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>belt_loop_stall</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>notify.type.belt_loop_stall.name</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>notify.type.belt_loop_stall.single</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>notify.type.belt_loop_stall.many</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>10</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>510</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>bottleneck</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>site_unreachable</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>notify.type.site_unreachable.name</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>notify.type.site_unreachable.single</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>notify.type.site_unreachable.many</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>520</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>buildings</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3202,6 +3202,106 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>override_offline</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>notify.type.override_offline.name</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>notify.type.override_offline.single</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>notify.type.override_offline.many</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>8</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>530</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>override_online</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>notify.type.override_online.name</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>notify.type.override_online.single</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>notify.type.override_online.many</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>8</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>540</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3302,6 +3302,56 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>research_stalled</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>notify.type.research_stalled.name</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>notify.type.research_stalled.single</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>notify.type.research_stalled.many</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>550</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3352,6 +3352,106 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>range_ended</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>notify.type.range_ended.name</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>notify.type.range_ended.single</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>notify.type.range_ended.many</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>8</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>560</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>range_target_unlocked</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>notify.type.range_target_unlocked.name</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>notify.type.range_target_unlocked.single</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>notify.type.range_target_unlocked.many</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>8</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>570</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3452,6 +3452,206 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>fusion_discovered</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_discovered.name</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_discovered.single</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_discovered.many</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>8</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>580</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>fusion_clue</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_clue.name</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_clue.single</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_clue.many</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>10</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>590</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>fusion_done</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_done.name</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_done.single</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_done.many</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>8</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>600</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>fusion_rolled_back</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_rolled_back.name</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_rolled_back.single</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>notify.type.fusion_rolled_back.many</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>610</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3652,6 +3652,156 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>intel_new</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>notify.type.intel_new.name</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>notify.type.intel_new.single</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>notify.type.intel_new.many</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>10</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>620</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>intel_raid</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>notify.type.intel_raid.name</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>notify.type.intel_raid.single</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>notify.type.intel_raid.many</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>15</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>630</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>raid</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>intel_interrupted</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>notify.type.intel_interrupted.name</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>notify.type.intel_interrupted.single</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>notify.type.intel_interrupted.many</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>10</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>640</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3802,6 +3802,56 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>blackbox_done</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>notify.type.blackbox_done.name</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>notify.type.blackbox_done.single</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>notify.type.blackbox_done.many</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>10</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>650</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3852,6 +3852,56 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>turret_supply</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>notify.type.turret_supply.name</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>notify.type.turret_supply.single</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>notify.type.turret_supply.many</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>10</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>660</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3902,6 +3902,106 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>shield_overload</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>notify.type.shield_overload.name</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>notify.type.shield_overload.single</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>notify.type.shield_overload.many</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>10</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>670</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>trap_supply</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>notify.type.trap_supply.name</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>notify.type.trap_supply.single</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>notify.type.trap_supply.many</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>10</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>680</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4002,6 +4002,156 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>drone_lost</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>notify.type.drone_lost.name</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>notify.type.drone_lost.single</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>notify.type.drone_lost.many</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>10</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>690</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>drone_crashed</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>notify.type.drone_crashed.name</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>notify.type.drone_crashed.single</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>notify.type.drone_crashed.many</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>10</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>700</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>drone_kits</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>notify.type.drone_kits.name</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>notify.type.drone_kits.single</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>notify.type.drone_kits.many</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>10</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>710</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4152,6 +4152,106 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>raid_warning</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>notify.type.raid_warning.name</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>notify.type.raid_warning.single</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>notify.type.raid_warning.many</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>15</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>720</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>raid</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>raid_withdrawn</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>notify.type.raid_withdrawn.name</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>notify.type.raid_withdrawn.single</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>notify.type.raid_withdrawn.many</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>10</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
+        <v>730</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>raid</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4252,6 +4252,156 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>raid_breach</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>notify.type.raid_breach.name</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>notify.type.raid_breach.single</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>notify.type.raid_breach.many</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>10</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>740</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>raid</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>raid_siege</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>notify.type.raid_siege.name</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>notify.type.raid_siege.single</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>notify.type.raid_siege.many</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>10</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>750</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>raid</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>raid_destroyed</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>notify.type.raid_destroyed.name</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>notify.type.raid_destroyed.single</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>notify.type.raid_destroyed.many</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>10</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>760</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>raid</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4402,6 +4402,56 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>raid_result</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>notify.type.raid_result.name</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>notify.type.raid_result.single</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>notify.type.raid_result.many</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>10</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>770</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>raid</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4452,6 +4452,56 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>difficulty_changed</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>notify.type.difficulty_changed.name</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>notify.type.difficulty_changed.single</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>notify.type.difficulty_changed.many</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>10</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>780</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4502,6 +4502,106 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>pipe_leak</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>notify.type.pipe_leak.name</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>notify.type.pipe_leak.single</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>notify.type.pipe_leak.many</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>10</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>790</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>leak_fire</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>notify.type.leak_fire.name</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>notify.type.leak_fire.single</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>notify.type.leak_fire.many</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>8</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="n">
+        <v>800</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4602,6 +4602,106 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>silent_night_warning</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>notify.type.silent_night_warning.name</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>notify.type.silent_night_warning.single</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>notify.type.silent_night_warning.many</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>10</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>810</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>silent_night_end</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>notify.type.silent_night_end.name</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>notify.type.silent_night_end.single</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>notify.type.silent_night_end.many</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>5</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>820</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4702,6 +4702,206 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>weather_warning</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>notify.type.weather_warning.name</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>notify.type.weather_warning.single</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>notify.type.weather_warning.many</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>10</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>830</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>weather_end</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>notify.type.weather_end.name</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>notify.type.weather_end.single</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>notify.type.weather_end.many</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>840</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>weather_damage</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>notify.type.weather_damage.name</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>notify.type.weather_damage.single</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>notify.type.weather_damage.many</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>8</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>850</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>pipe_frozen</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>notify.type.pipe_frozen.name</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>notify.type.pipe_frozen.single</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>notify.type.pipe_frozen.many</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>8</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>860</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4902,6 +4902,256 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>purify_milestone</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>notify.type.purify_milestone.name</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>notify.type.purify_milestone.single</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>notify.type.purify_milestone.many</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>5</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>870</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>core_memo</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>notify.type.core_memo.name</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>notify.type.core_memo.single</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>notify.type.core_memo.many</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>880</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>purify_stalled</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>notify.type.purify_stalled.name</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>notify.type.purify_stalled.single</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>notify.type.purify_stalled.many</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>10</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>890</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>pollution_raised</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>notify.type.pollution_raised.name</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>notify.type.pollution_raised.single</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>notify.type.pollution_raised.many</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>8</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>900</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>contamination_cleared</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>notify.type.contamination_cleared.name</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>notify.type.contamination_cleared.single</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>notify.type.contamination_cleared.many</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>8</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>910</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5152,6 +5152,156 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>relic_found</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>notify.type.relic_found.name</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>notify.type.relic_found.single</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>notify.type.relic_found.many</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>8</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>920</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>relic_recovered</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>notify.type.relic_recovered.name</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>notify.type.relic_recovered.single</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>notify.type.relic_recovered.many</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>8</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>930</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>hazard_found</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>notify.type.hazard_found.name</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>notify.type.hazard_found.single</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>notify.type.hazard_found.many</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>8</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>940</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5302,6 +5302,106 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>expedition_march</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>notify.type.expedition_march.name</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>notify.type.expedition_march.single</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>notify.type.expedition_march.many</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ExpeditionMarchArrived|ExpeditionMarchReturned</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>5</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>950</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>expedition_alert</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>notify.type.expedition_alert.name</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>notify.type.expedition_alert.single</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>notify.type.expedition_alert.many</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ExpeditionMarchHalted|ExpeditionMarchArrivalFailed|ExpeditionMarchEncounter|ExpeditionMarchHazard|ExpeditionMarchEdge</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>6</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" t="n">
+        <v>960</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5402,6 +5402,156 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>territory_entered</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>notify.type.territory_entered.name</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>notify.type.territory_entered.single</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>notify.type.territory_entered.many</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ExpeditionMarchTerritory</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>6</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" t="n">
+        <v>970</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>poi_found</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>notify.type.poi_found.name</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>notify.type.poi_found.single</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>notify.type.poi_found.many</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>8</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>980</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>interior_transit</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>notify.type.interior_transit.name</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>notify.type.interior_transit.single</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>notify.type.interior_transit.many</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>InteriorEnter|InteriorExit</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>4</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
+        <v>990</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5552,6 +5552,106 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>territory_status</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>notify.type.territory_status.name</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>notify.type.territory_status.single</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>notify.type.territory_status.many</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>6</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>territory_alert</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>notify.type.territory_alert.name</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>notify.type.territory_alert.single</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>notify.type.territory_alert.many</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>6</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>raid</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4156,27 +4156,27 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>raid_warning</t>
+          <t>drop_landed</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>notify.type.raid_warning.name</t>
+          <t>notify.type.drop_landed.name</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>notify.type.raid_warning.single</t>
+          <t>notify.type.drop_landed.single</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>notify.type.raid_warning.many</t>
+          <t>notify.type.drop_landed.many</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J75" t="n">
         <v>1</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>raid</t>
+          <t>event</t>
         </is>
       </c>
     </row>
@@ -4206,27 +4206,27 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>raid_withdrawn</t>
+          <t>drop_alert</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>notify.type.raid_withdrawn.name</t>
+          <t>notify.type.drop_alert.name</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>notify.type.raid_withdrawn.single</t>
+          <t>notify.type.drop_alert.single</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>notify.type.raid_withdrawn.many</t>
+          <t>notify.type.drop_alert.many</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>raid</t>
+          <t>event</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>raid_breach</t>
+          <t>raid_warning</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>notify.type.raid_breach.name</t>
+          <t>notify.type.raid_warning.name</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>notify.type.raid_breach.single</t>
+          <t>notify.type.raid_warning.single</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>notify.type.raid_breach.many</t>
+          <t>notify.type.raid_warning.many</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -4306,7 +4306,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>raid_siege</t>
+          <t>raid_withdrawn</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>notify.type.raid_siege.name</t>
+          <t>notify.type.raid_withdrawn.name</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>notify.type.raid_siege.single</t>
+          <t>notify.type.raid_withdrawn.single</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>notify.type.raid_siege.many</t>
+          <t>notify.type.raid_withdrawn.many</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4356,27 +4356,27 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>raid_destroyed</t>
+          <t>raid_breach</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>notify.type.raid_destroyed.name</t>
+          <t>notify.type.raid_breach.name</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>notify.type.raid_destroyed.single</t>
+          <t>notify.type.raid_breach.single</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>notify.type.raid_destroyed.many</t>
+          <t>notify.type.raid_breach.many</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4406,7 +4406,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>raid_result</t>
+          <t>raid_siege</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4416,17 +4416,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>notify.type.raid_result.name</t>
+          <t>notify.type.raid_siege.name</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>notify.type.raid_result.single</t>
+          <t>notify.type.raid_siege.single</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>notify.type.raid_result.many</t>
+          <t>notify.type.raid_siege.many</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4456,7 +4456,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>difficulty_changed</t>
+          <t>raid_destroyed</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>notify.type.difficulty_changed.name</t>
+          <t>notify.type.raid_destroyed.name</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>notify.type.difficulty_changed.single</t>
+          <t>notify.type.raid_destroyed.single</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>notify.type.difficulty_changed.many</t>
+          <t>notify.type.raid_destroyed.many</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>raid</t>
         </is>
       </c>
     </row>
@@ -4506,27 +4506,27 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>pipe_leak</t>
+          <t>raid_result</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>notify.type.pipe_leak.name</t>
+          <t>notify.type.raid_result.name</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>notify.type.pipe_leak.single</t>
+          <t>notify.type.raid_result.single</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>notify.type.pipe_leak.many</t>
+          <t>notify.type.raid_result.many</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>buildings</t>
+          <t>raid</t>
         </is>
       </c>
     </row>
@@ -4556,27 +4556,27 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>leak_fire</t>
+          <t>difficulty_changed</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>notify.type.leak_fire.name</t>
+          <t>notify.type.difficulty_changed.name</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>notify.type.leak_fire.single</t>
+          <t>notify.type.difficulty_changed.single</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>notify.type.leak_fire.many</t>
+          <t>notify.type.difficulty_changed.many</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>buildings</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>silent_night_warning</t>
+          <t>pipe_leak</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_warning.name</t>
+          <t>notify.type.pipe_leak.name</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_warning.single</t>
+          <t>notify.type.pipe_leak.single</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_warning.many</t>
+          <t>notify.type.pipe_leak.many</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>buildings</t>
         </is>
       </c>
     </row>
@@ -4656,27 +4656,27 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>silent_night_end</t>
+          <t>leak_fire</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_end.name</t>
+          <t>notify.type.leak_fire.name</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_end.single</t>
+          <t>notify.type.leak_fire.single</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_end.many</t>
+          <t>notify.type.leak_fire.many</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J85" t="n">
         <v>1</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>buildings</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>weather_warning</t>
+          <t>silent_night_warning</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4716,17 +4716,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>notify.type.weather_warning.name</t>
+          <t>notify.type.silent_night_warning.name</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>notify.type.weather_warning.single</t>
+          <t>notify.type.silent_night_warning.single</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>notify.type.weather_warning.many</t>
+          <t>notify.type.silent_night_warning.many</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4756,7 +4756,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>weather_end</t>
+          <t>silent_night_end</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>notify.type.weather_end.name</t>
+          <t>notify.type.silent_night_end.name</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>notify.type.weather_end.single</t>
+          <t>notify.type.silent_night_end.single</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>notify.type.weather_end.many</t>
+          <t>notify.type.silent_night_end.many</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4806,7 +4806,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>weather_damage</t>
+          <t>weather_warning</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4816,17 +4816,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>notify.type.weather_damage.name</t>
+          <t>notify.type.weather_warning.name</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>notify.type.weather_damage.single</t>
+          <t>notify.type.weather_warning.single</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>notify.type.weather_damage.many</t>
+          <t>notify.type.weather_warning.many</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J88" t="n">
         <v>1</v>
@@ -4856,27 +4856,27 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>pipe_frozen</t>
+          <t>weather_end</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>notify.type.pipe_frozen.name</t>
+          <t>notify.type.weather_end.name</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>notify.type.pipe_frozen.single</t>
+          <t>notify.type.weather_end.single</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>notify.type.pipe_frozen.many</t>
+          <t>notify.type.weather_end.many</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -4906,27 +4906,27 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>purify_milestone</t>
+          <t>weather_damage</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>notify.type.purify_milestone.name</t>
+          <t>notify.type.weather_damage.name</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>notify.type.purify_milestone.single</t>
+          <t>notify.type.weather_damage.single</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>notify.type.purify_milestone.many</t>
+          <t>notify.type.weather_damage.many</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J90" t="n">
         <v>1</v>
@@ -4956,27 +4956,27 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>core_memo</t>
+          <t>pipe_frozen</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>notify.type.core_memo.name</t>
+          <t>notify.type.pipe_frozen.name</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>notify.type.core_memo.single</t>
+          <t>notify.type.pipe_frozen.single</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>notify.type.core_memo.many</t>
+          <t>notify.type.pipe_frozen.many</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J91" t="n">
         <v>1</v>
@@ -5006,27 +5006,27 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>purify_stalled</t>
+          <t>purify_milestone</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>notify.type.purify_stalled.name</t>
+          <t>notify.type.purify_milestone.name</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>notify.type.purify_stalled.single</t>
+          <t>notify.type.purify_milestone.single</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>notify.type.purify_stalled.many</t>
+          <t>notify.type.purify_milestone.many</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
@@ -5056,27 +5056,27 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>pollution_raised</t>
+          <t>core_memo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>notify.type.pollution_raised.name</t>
+          <t>notify.type.core_memo.name</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>notify.type.pollution_raised.single</t>
+          <t>notify.type.core_memo.single</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>notify.type.pollution_raised.many</t>
+          <t>notify.type.core_memo.many</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5088,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J93" t="n">
         <v>1</v>
@@ -5106,27 +5106,27 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>contamination_cleared</t>
+          <t>purify_stalled</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>notify.type.contamination_cleared.name</t>
+          <t>notify.type.purify_stalled.name</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>notify.type.contamination_cleared.single</t>
+          <t>notify.type.purify_stalled.single</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>notify.type.contamination_cleared.many</t>
+          <t>notify.type.purify_stalled.many</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5138,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J94" t="n">
         <v>1</v>
@@ -5156,27 +5156,27 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>relic_found</t>
+          <t>pollution_raised</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>notify.type.relic_found.name</t>
+          <t>notify.type.pollution_raised.name</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>notify.type.relic_found.single</t>
+          <t>notify.type.pollution_raised.single</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>notify.type.relic_found.many</t>
+          <t>notify.type.pollution_raised.many</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>weather</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>relic_recovered</t>
+          <t>contamination_cleared</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5216,17 +5216,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>notify.type.relic_recovered.name</t>
+          <t>notify.type.contamination_cleared.name</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>notify.type.relic_recovered.single</t>
+          <t>notify.type.contamination_cleared.single</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>notify.type.relic_recovered.many</t>
+          <t>notify.type.contamination_cleared.many</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>weather</t>
         </is>
       </c>
     </row>
@@ -5256,27 +5256,27 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>hazard_found</t>
+          <t>relic_found</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>notify.type.hazard_found.name</t>
+          <t>notify.type.relic_found.name</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>notify.type.hazard_found.single</t>
+          <t>notify.type.relic_found.single</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>notify.type.hazard_found.many</t>
+          <t>notify.type.relic_found.many</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5306,7 +5306,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>expedition_march</t>
+          <t>relic_recovered</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5316,29 +5316,29 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>notify.type.expedition_march.name</t>
+          <t>notify.type.relic_recovered.name</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>notify.type.expedition_march.single</t>
+          <t>notify.type.relic_recovered.single</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>notify.type.expedition_march.many</t>
+          <t>notify.type.relic_recovered.many</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ExpeditionMarchArrived|ExpeditionMarchReturned</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>research</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>expedition_alert</t>
+          <t>hazard_found</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5366,29 +5366,29 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>notify.type.expedition_alert.name</t>
+          <t>notify.type.hazard_found.name</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>notify.type.expedition_alert.single</t>
+          <t>notify.type.hazard_found.single</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>notify.type.expedition_alert.many</t>
+          <t>notify.type.hazard_found.many</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ExpeditionMarchHalted|ExpeditionMarchArrivalFailed|ExpeditionMarchEncounter|ExpeditionMarchHazard|ExpeditionMarchEdge</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J99" t="n">
         <v>1</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>event</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>territory_entered</t>
+          <t>expedition_march</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5416,29 +5416,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>notify.type.territory_entered.name</t>
+          <t>notify.type.expedition_march.name</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>notify.type.territory_entered.single</t>
+          <t>notify.type.expedition_march.single</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>notify.type.territory_entered.many</t>
+          <t>notify.type.expedition_march.many</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ExpeditionMarchTerritory</t>
+          <t>ExpeditionMarchArrived|ExpeditionMarchReturned</t>
         </is>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
         <v>1</v>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -5456,39 +5456,39 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>poi_found</t>
+          <t>expedition_alert</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>notify.type.poi_found.name</t>
+          <t>notify.type.expedition_alert.name</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>notify.type.poi_found.single</t>
+          <t>notify.type.expedition_alert.single</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>notify.type.poi_found.many</t>
+          <t>notify.type.expedition_alert.many</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ExpeditionMarchHalted|ExpeditionMarchArrivalFailed|ExpeditionMarchEncounter|ExpeditionMarchHazard|ExpeditionMarchEdge</t>
         </is>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J101" t="n">
         <v>1</v>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>interior_transit</t>
+          <t>territory_entered</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5516,29 +5516,29 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>notify.type.interior_transit.name</t>
+          <t>notify.type.territory_entered.name</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>notify.type.interior_transit.single</t>
+          <t>notify.type.territory_entered.single</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>notify.type.interior_transit.many</t>
+          <t>notify.type.territory_entered.many</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>InteriorEnter|InteriorExit</t>
+          <t>ExpeditionMarchTerritory</t>
         </is>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J102" t="n">
         <v>1</v>
@@ -5556,7 +5556,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>territory_status</t>
+          <t>poi_found</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>notify.type.territory_status.name</t>
+          <t>notify.type.poi_found.name</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>notify.type.territory_status.single</t>
+          <t>notify.type.poi_found.single</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>notify.type.territory_status.many</t>
+          <t>notify.type.poi_found.many</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5588,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J103" t="n">
         <v>1</v>
@@ -5606,39 +5606,39 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>territory_alert</t>
+          <t>interior_transit</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>notify.type.territory_alert.name</t>
+          <t>notify.type.interior_transit.name</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>notify.type.territory_alert.single</t>
+          <t>notify.type.interior_transit.single</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>notify.type.territory_alert.many</t>
+          <t>notify.type.interior_transit.many</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>InteriorEnter|InteriorExit</t>
         </is>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
         <v>1</v>
@@ -5647,6 +5647,106 @@
         <v>1010</v>
       </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>territory_status</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>notify.type.territory_status.name</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>notify.type.territory_status.single</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>notify.type.territory_status.many</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>6</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1020</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>territory_alert</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>notify.type.territory_alert.name</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>notify.type.territory_alert.single</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>notify.type.territory_alert.many</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>6</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1030</v>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t>raid</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4256,27 +4256,27 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>raid_warning</t>
+          <t>outpost_founded</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>notify.type.raid_warning.name</t>
+          <t>notify.type.outpost_founded.name</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>notify.type.raid_warning.single</t>
+          <t>notify.type.outpost_founded.single</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>notify.type.raid_warning.many</t>
+          <t>notify.type.outpost_founded.many</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>raid</t>
+          <t>event</t>
         </is>
       </c>
     </row>
@@ -4306,27 +4306,27 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>raid_withdrawn</t>
+          <t>outpost_wiped</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>notify.type.raid_withdrawn.name</t>
+          <t>notify.type.outpost_wiped.name</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>notify.type.raid_withdrawn.single</t>
+          <t>notify.type.outpost_wiped.single</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>notify.type.raid_withdrawn.many</t>
+          <t>notify.type.outpost_wiped.many</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4356,7 +4356,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>raid_breach</t>
+          <t>outpost_removed</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>notify.type.raid_breach.name</t>
+          <t>notify.type.outpost_removed.name</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>notify.type.raid_breach.single</t>
+          <t>notify.type.outpost_removed.single</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>notify.type.raid_breach.many</t>
+          <t>notify.type.outpost_removed.many</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>raid</t>
+          <t>buildings</t>
         </is>
       </c>
     </row>
@@ -4406,27 +4406,27 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>raid_siege</t>
+          <t>raid_warning</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>notify.type.raid_siege.name</t>
+          <t>notify.type.raid_warning.name</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>notify.type.raid_siege.single</t>
+          <t>notify.type.raid_warning.single</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>notify.type.raid_siege.many</t>
+          <t>notify.type.raid_warning.many</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J80" t="n">
         <v>1</v>
@@ -4456,7 +4456,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>raid_destroyed</t>
+          <t>raid_withdrawn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>notify.type.raid_destroyed.name</t>
+          <t>notify.type.raid_withdrawn.name</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>notify.type.raid_destroyed.single</t>
+          <t>notify.type.raid_withdrawn.single</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>notify.type.raid_destroyed.many</t>
+          <t>notify.type.raid_withdrawn.many</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4506,27 +4506,27 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>raid_result</t>
+          <t>raid_breach</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>notify.type.raid_result.name</t>
+          <t>notify.type.raid_breach.name</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>notify.type.raid_result.single</t>
+          <t>notify.type.raid_breach.single</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>notify.type.raid_result.many</t>
+          <t>notify.type.raid_breach.many</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4556,7 +4556,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>difficulty_changed</t>
+          <t>raid_siege</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4566,17 +4566,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>notify.type.difficulty_changed.name</t>
+          <t>notify.type.raid_siege.name</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>notify.type.difficulty_changed.single</t>
+          <t>notify.type.raid_siege.single</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>notify.type.difficulty_changed.many</t>
+          <t>notify.type.raid_siege.many</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>raid</t>
         </is>
       </c>
     </row>
@@ -4606,27 +4606,27 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>pipe_leak</t>
+          <t>raid_destroyed</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>notify.type.pipe_leak.name</t>
+          <t>notify.type.raid_destroyed.name</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>notify.type.pipe_leak.single</t>
+          <t>notify.type.raid_destroyed.single</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>notify.type.pipe_leak.many</t>
+          <t>notify.type.raid_destroyed.many</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>buildings</t>
+          <t>raid</t>
         </is>
       </c>
     </row>
@@ -4656,27 +4656,27 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>leak_fire</t>
+          <t>raid_result</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>notify.type.leak_fire.name</t>
+          <t>notify.type.raid_result.name</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>notify.type.leak_fire.single</t>
+          <t>notify.type.raid_result.single</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>notify.type.leak_fire.many</t>
+          <t>notify.type.raid_result.many</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J85" t="n">
         <v>1</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>buildings</t>
+          <t>raid</t>
         </is>
       </c>
     </row>
@@ -4706,27 +4706,27 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>silent_night_warning</t>
+          <t>difficulty_changed</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_warning.name</t>
+          <t>notify.type.difficulty_changed.name</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_warning.single</t>
+          <t>notify.type.difficulty_changed.single</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_warning.many</t>
+          <t>notify.type.difficulty_changed.many</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -4756,27 +4756,27 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>silent_night_end</t>
+          <t>pipe_leak</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_end.name</t>
+          <t>notify.type.pipe_leak.name</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_end.single</t>
+          <t>notify.type.pipe_leak.single</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>notify.type.silent_night_end.many</t>
+          <t>notify.type.pipe_leak.many</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J87" t="n">
         <v>1</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>buildings</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>weather_warning</t>
+          <t>leak_fire</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4816,17 +4816,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>notify.type.weather_warning.name</t>
+          <t>notify.type.leak_fire.name</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>notify.type.weather_warning.single</t>
+          <t>notify.type.leak_fire.single</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>notify.type.weather_warning.many</t>
+          <t>notify.type.leak_fire.many</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
         <v>1</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>buildings</t>
         </is>
       </c>
     </row>
@@ -4856,27 +4856,27 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>weather_end</t>
+          <t>silent_night_warning</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>notify.type.weather_end.name</t>
+          <t>notify.type.silent_night_warning.name</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>notify.type.weather_end.single</t>
+          <t>notify.type.silent_night_warning.single</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>notify.type.weather_end.many</t>
+          <t>notify.type.silent_night_warning.many</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -4906,27 +4906,27 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>weather_damage</t>
+          <t>silent_night_end</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>notify.type.weather_damage.name</t>
+          <t>notify.type.silent_night_end.name</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>notify.type.weather_damage.single</t>
+          <t>notify.type.silent_night_end.single</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>notify.type.weather_damage.many</t>
+          <t>notify.type.silent_night_end.many</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
         <v>1</v>
@@ -4956,7 +4956,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>pipe_frozen</t>
+          <t>weather_warning</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4966,17 +4966,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>notify.type.pipe_frozen.name</t>
+          <t>notify.type.weather_warning.name</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>notify.type.pipe_frozen.single</t>
+          <t>notify.type.weather_warning.single</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>notify.type.pipe_frozen.many</t>
+          <t>notify.type.weather_warning.many</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J91" t="n">
         <v>1</v>
@@ -5006,7 +5006,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>purify_milestone</t>
+          <t>weather_end</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>notify.type.purify_milestone.name</t>
+          <t>notify.type.weather_end.name</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>notify.type.purify_milestone.single</t>
+          <t>notify.type.weather_end.single</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>notify.type.purify_milestone.many</t>
+          <t>notify.type.weather_end.many</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5056,27 +5056,27 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>core_memo</t>
+          <t>weather_damage</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>notify.type.core_memo.name</t>
+          <t>notify.type.weather_damage.name</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>notify.type.core_memo.single</t>
+          <t>notify.type.weather_damage.single</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>notify.type.core_memo.many</t>
+          <t>notify.type.weather_damage.many</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5088,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J93" t="n">
         <v>1</v>
@@ -5106,7 +5106,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>purify_stalled</t>
+          <t>pipe_frozen</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5116,17 +5116,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>notify.type.purify_stalled.name</t>
+          <t>notify.type.pipe_frozen.name</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>notify.type.purify_stalled.single</t>
+          <t>notify.type.pipe_frozen.single</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>notify.type.purify_stalled.many</t>
+          <t>notify.type.pipe_frozen.many</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5138,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J94" t="n">
         <v>1</v>
@@ -5156,27 +5156,27 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>pollution_raised</t>
+          <t>purify_milestone</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>notify.type.pollution_raised.name</t>
+          <t>notify.type.purify_milestone.name</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>notify.type.pollution_raised.single</t>
+          <t>notify.type.purify_milestone.single</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>notify.type.pollution_raised.many</t>
+          <t>notify.type.purify_milestone.many</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5188,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
         <v>1</v>
@@ -5206,7 +5206,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>contamination_cleared</t>
+          <t>core_memo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5216,17 +5216,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>notify.type.contamination_cleared.name</t>
+          <t>notify.type.core_memo.name</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>notify.type.contamination_cleared.single</t>
+          <t>notify.type.core_memo.single</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>notify.type.contamination_cleared.many</t>
+          <t>notify.type.core_memo.many</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5238,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J96" t="n">
         <v>1</v>
@@ -5256,27 +5256,27 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>relic_found</t>
+          <t>purify_stalled</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>notify.type.relic_found.name</t>
+          <t>notify.type.purify_stalled.name</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>notify.type.relic_found.single</t>
+          <t>notify.type.purify_stalled.single</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>notify.type.relic_found.many</t>
+          <t>notify.type.purify_stalled.many</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J97" t="n">
         <v>1</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>weather</t>
         </is>
       </c>
     </row>
@@ -5306,27 +5306,27 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>relic_recovered</t>
+          <t>pollution_raised</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>notify.type.relic_recovered.name</t>
+          <t>notify.type.pollution_raised.name</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>notify.type.relic_recovered.single</t>
+          <t>notify.type.pollution_raised.single</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>notify.type.relic_recovered.many</t>
+          <t>notify.type.pollution_raised.many</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>weather</t>
         </is>
       </c>
     </row>
@@ -5356,27 +5356,27 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>hazard_found</t>
+          <t>contamination_cleared</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>notify.type.hazard_found.name</t>
+          <t>notify.type.contamination_cleared.name</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>notify.type.hazard_found.single</t>
+          <t>notify.type.contamination_cleared.single</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>notify.type.hazard_found.many</t>
+          <t>notify.type.contamination_cleared.many</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>weather</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>expedition_march</t>
+          <t>relic_found</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5416,29 +5416,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>notify.type.expedition_march.name</t>
+          <t>notify.type.relic_found.name</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>notify.type.expedition_march.single</t>
+          <t>notify.type.relic_found.single</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>notify.type.expedition_march.many</t>
+          <t>notify.type.relic_found.many</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ExpeditionMarchArrived|ExpeditionMarchReturned</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J100" t="n">
         <v>1</v>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>event</t>
         </is>
       </c>
     </row>
@@ -5456,39 +5456,39 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>expedition_alert</t>
+          <t>relic_recovered</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>notify.type.expedition_alert.name</t>
+          <t>notify.type.relic_recovered.name</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>notify.type.expedition_alert.single</t>
+          <t>notify.type.relic_recovered.single</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>notify.type.expedition_alert.many</t>
+          <t>notify.type.relic_recovered.many</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ExpeditionMarchHalted|ExpeditionMarchArrivalFailed|ExpeditionMarchEncounter|ExpeditionMarchHazard|ExpeditionMarchEdge</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J101" t="n">
         <v>1</v>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>research</t>
         </is>
       </c>
     </row>
@@ -5506,39 +5506,39 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>territory_entered</t>
+          <t>hazard_found</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>notify.type.territory_entered.name</t>
+          <t>notify.type.hazard_found.name</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>notify.type.territory_entered.single</t>
+          <t>notify.type.hazard_found.single</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>notify.type.territory_entered.many</t>
+          <t>notify.type.hazard_found.many</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ExpeditionMarchTerritory</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J102" t="n">
         <v>1</v>
@@ -5556,7 +5556,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>poi_found</t>
+          <t>expedition_march</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5566,29 +5566,29 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>notify.type.poi_found.name</t>
+          <t>notify.type.expedition_march.name</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>notify.type.poi_found.single</t>
+          <t>notify.type.expedition_march.single</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>notify.type.poi_found.many</t>
+          <t>notify.type.expedition_march.many</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ExpeditionMarchArrived|ExpeditionMarchReturned</t>
         </is>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J103" t="n">
         <v>1</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -5606,39 +5606,39 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>interior_transit</t>
+          <t>expedition_alert</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>notify.type.interior_transit.name</t>
+          <t>notify.type.expedition_alert.name</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>notify.type.interior_transit.single</t>
+          <t>notify.type.expedition_alert.single</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>notify.type.interior_transit.many</t>
+          <t>notify.type.expedition_alert.many</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>InteriorEnter|InteriorExit</t>
+          <t>ExpeditionMarchHalted|ExpeditionMarchArrivalFailed|ExpeditionMarchEncounter|ExpeditionMarchHazard|ExpeditionMarchEdge</t>
         </is>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J104" t="n">
         <v>1</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>territory_status</t>
+          <t>territory_entered</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5666,22 +5666,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>notify.type.territory_status.name</t>
+          <t>notify.type.territory_entered.name</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>notify.type.territory_status.single</t>
+          <t>notify.type.territory_entered.single</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>notify.type.territory_status.many</t>
+          <t>notify.type.territory_entered.many</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ExpeditionMarchTerritory</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -5706,27 +5706,27 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>territory_alert</t>
+          <t>poi_found</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>notify.type.territory_alert.name</t>
+          <t>notify.type.poi_found.name</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>notify.type.territory_alert.single</t>
+          <t>notify.type.poi_found.single</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>notify.type.territory_alert.many</t>
+          <t>notify.type.poi_found.many</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5738,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J106" t="n">
         <v>1</v>
@@ -5747,6 +5747,156 @@
         <v>1030</v>
       </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>interior_transit</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>notify.type.interior_transit.name</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>notify.type.interior_transit.single</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>notify.type.interior_transit.many</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>InteriorEnter|InteriorExit</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>4</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1040</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>territory_status</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>notify.type.territory_status.name</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>notify.type.territory_status.single</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>notify.type.territory_status.many</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>6</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1050</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>territory_alert</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>notify.type.territory_alert.name</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>notify.type.territory_alert.single</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>notify.type.territory_alert.many</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>6</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1060</v>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t>raid</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5902,6 +5902,56 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>loot_packet</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>notify.type.loot_packet.name</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>notify.type.loot_packet.single</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>notify.type.loot_packet.many</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>6</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1070</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5952,6 +5952,56 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>cargo</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>notify.type.cargo.name</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>notify.type.cargo.single</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>notify.type.cargo.many</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>6</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6002,6 +6002,106 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>quest</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>notify.type.quest.name</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>notify.type.quest.single</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>notify.type.quest.many</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>QuestNew|QuestComplete|QuestUpdate</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>5</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1090</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>quest_alert</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>notify.type.quest_alert.name</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>notify.type.quest_alert.single</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>notify.type.quest_alert.many</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>QuestAlert</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>5</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6102,6 +6102,56 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>heritage</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>notify.type.heritage.name</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>notify.type.heritage.single</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>notify.type.heritage.many</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>8</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1110</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6152,6 +6152,56 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>loot_expiry</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>notify.type.loot_expiry.name</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>notify.type.loot_expiry.single</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>notify.type.loot_expiry.many</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>8</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6202,6 +6202,56 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>content_error</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.name</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.single</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.many</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>10</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1130</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6206,27 +6206,27 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>content_error</t>
+          <t>narrative_new</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>notify.type.content_error.name</t>
+          <t>notify.type.narrative_new.name</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>notify.type.content_error.single</t>
+          <t>notify.type.narrative_new.single</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>notify.type.content_error.many</t>
+          <t>notify.type.narrative_new.many</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6238,7 +6238,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J116" t="n">
         <v>1</v>
@@ -6247,6 +6247,56 @@
         <v>1130</v>
       </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>content_error</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.name</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.single</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.many</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>10</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:L119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6256,7 +6256,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>content_error</t>
+          <t>silent_boss</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6266,17 +6266,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>notify.type.content_error.name</t>
+          <t>notify.type.silent_boss.name</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>notify.type.content_error.single</t>
+          <t>notify.type.silent_boss.single</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>notify.type.content_error.many</t>
+          <t>notify.type.silent_boss.many</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -6288,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J117" t="n">
         <v>1</v>
@@ -6297,6 +6297,106 @@
         <v>1140</v>
       </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>emi_noise</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>notify.type.emi_noise.name</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>notify.type.emi_noise.single</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>notify.type.emi_noise.many</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>10</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>content_error</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.name</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.single</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.many</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>10</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1160</v>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L119"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6356,7 +6356,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>content_error</t>
+          <t>foundry_boss</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>notify.type.content_error.name</t>
+          <t>notify.type.foundry_boss.name</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>notify.type.content_error.single</t>
+          <t>notify.type.foundry_boss.single</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>notify.type.content_error.many</t>
+          <t>notify.type.foundry_boss.many</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6388,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J119" t="n">
         <v>1</v>
@@ -6397,6 +6397,106 @@
         <v>1160</v>
       </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>slag_heat</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>notify.type.slag_heat.name</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>notify.type.slag_heat.single</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>notify.type.slag_heat.many</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>10</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1170</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>content_error</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.name</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.single</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.many</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>10</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1180</v>
+      </c>
+      <c r="L121" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6502,6 +6502,56 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>codex_new</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.name</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.single</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.many</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>8</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:L124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6456,27 +6456,27 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>content_error</t>
+          <t>pace_open</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>notify.type.content_error.name</t>
+          <t>notify.type.pace_open.name</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>notify.type.content_error.single</t>
+          <t>notify.type.pace_open.single</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>notify.type.content_error.many</t>
+          <t>notify.type.pace_open.many</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J121" t="n">
         <v>1</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>event</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>codex_new</t>
+          <t>signal_contact</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.name</t>
+          <t>notify.type.signal_contact.name</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.single</t>
+          <t>notify.type.signal_contact.single</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.many</t>
+          <t>notify.type.signal_contact.many</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -6538,7 +6538,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J122" t="n">
         <v>1</v>
@@ -6547,6 +6547,106 @@
         <v>1190</v>
       </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>content_error</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.name</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.single</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.many</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>10</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>codex_new</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.name</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.single</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.many</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>8</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1210</v>
+      </c>
+      <c r="L124" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L124"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6556,7 +6556,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>content_error</t>
+          <t>acid_marsh</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>notify.type.content_error.name</t>
+          <t>notify.type.acid_marsh.name</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>notify.type.content_error.single</t>
+          <t>notify.type.acid_marsh.single</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>notify.type.content_error.many</t>
+          <t>notify.type.acid_marsh.many</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -6606,7 +6606,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>codex_new</t>
+          <t>clarity_counter</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.name</t>
+          <t>notify.type.clarity_counter.name</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.single</t>
+          <t>notify.type.clarity_counter.single</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.many</t>
+          <t>notify.type.clarity_counter.many</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J124" t="n">
         <v>1</v>
@@ -6647,6 +6647,106 @@
         <v>1210</v>
       </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>content_error</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.name</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.single</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.many</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>10</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1220</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>codex_new</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.name</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.single</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.many</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>8</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1230</v>
+      </c>
+      <c r="L126" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L126"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6606,7 +6606,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>clarity_counter</t>
+          <t>territory_intro</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>notify.type.clarity_counter.name</t>
+          <t>notify.type.territory_intro.name</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>notify.type.clarity_counter.single</t>
+          <t>notify.type.territory_intro.single</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>notify.type.clarity_counter.many</t>
+          <t>notify.type.territory_intro.many</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -6656,27 +6656,27 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>content_error</t>
+          <t>acid_coating</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>notify.type.content_error.name</t>
+          <t>notify.type.acid_coating.name</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>notify.type.content_error.single</t>
+          <t>notify.type.acid_coating.single</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>notify.type.content_error.many</t>
+          <t>notify.type.acid_coating.many</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -6706,7 +6706,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>codex_new</t>
+          <t>clarity_counter</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6716,17 +6716,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.name</t>
+          <t>notify.type.clarity_counter.name</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.single</t>
+          <t>notify.type.clarity_counter.single</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.many</t>
+          <t>notify.type.clarity_counter.many</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -6738,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J126" t="n">
         <v>1</v>
@@ -6747,6 +6747,106 @@
         <v>1230</v>
       </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>content_error</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.name</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.single</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.many</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>10</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>codex_new</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.name</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.single</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.many</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>8</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6656,7 +6656,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>acid_coating</t>
+          <t>reaction_batch</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6666,17 +6666,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>notify.type.acid_coating.name</t>
+          <t>notify.type.reaction_batch.name</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>notify.type.acid_coating.single</t>
+          <t>notify.type.reaction_batch.single</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>notify.type.acid_coating.many</t>
+          <t>notify.type.reaction_batch.many</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -6706,7 +6706,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>clarity_counter</t>
+          <t>acid_coating</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6716,17 +6716,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>notify.type.clarity_counter.name</t>
+          <t>notify.type.acid_coating.name</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>notify.type.clarity_counter.single</t>
+          <t>notify.type.acid_coating.single</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>notify.type.clarity_counter.many</t>
+          <t>notify.type.acid_coating.many</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -6756,27 +6756,27 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>content_error</t>
+          <t>clarity_counter</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>notify.type.content_error.name</t>
+          <t>notify.type.clarity_counter.name</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>notify.type.content_error.single</t>
+          <t>notify.type.clarity_counter.single</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>notify.type.content_error.many</t>
+          <t>notify.type.clarity_counter.many</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -6806,27 +6806,27 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>codex_new</t>
+          <t>content_error</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.name</t>
+          <t>notify.type.content_error.name</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.single</t>
+          <t>notify.type.content_error.single</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.many</t>
+          <t>notify.type.content_error.many</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J128" t="n">
         <v>1</v>
@@ -6847,6 +6847,56 @@
         <v>1250</v>
       </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>codex_new</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.name</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.single</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.many</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>8</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L129" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6656,27 +6656,27 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>reaction_batch</t>
+          <t>clarity_boss</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>notify.type.reaction_batch.name</t>
+          <t>notify.type.clarity_boss.name</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>notify.type.reaction_batch.single</t>
+          <t>notify.type.clarity_boss.single</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>notify.type.reaction_batch.many</t>
+          <t>notify.type.clarity_boss.many</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J125" t="n">
         <v>1</v>
@@ -6706,7 +6706,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>acid_coating</t>
+          <t>reaction_batch</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6716,17 +6716,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>notify.type.acid_coating.name</t>
+          <t>notify.type.reaction_batch.name</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>notify.type.acid_coating.single</t>
+          <t>notify.type.reaction_batch.single</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>notify.type.acid_coating.many</t>
+          <t>notify.type.reaction_batch.many</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -6756,7 +6756,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>clarity_counter</t>
+          <t>acid_coating</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6766,17 +6766,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>notify.type.clarity_counter.name</t>
+          <t>notify.type.acid_coating.name</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>notify.type.clarity_counter.single</t>
+          <t>notify.type.acid_coating.single</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>notify.type.clarity_counter.many</t>
+          <t>notify.type.acid_coating.many</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -6806,27 +6806,27 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>content_error</t>
+          <t>clarity_counter</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>notify.type.content_error.name</t>
+          <t>notify.type.clarity_counter.name</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>notify.type.content_error.single</t>
+          <t>notify.type.clarity_counter.single</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>notify.type.content_error.many</t>
+          <t>notify.type.clarity_counter.many</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -6856,27 +6856,27 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>codex_new</t>
+          <t>content_error</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.name</t>
+          <t>notify.type.content_error.name</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.single</t>
+          <t>notify.type.content_error.single</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.many</t>
+          <t>notify.type.content_error.many</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -6888,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J129" t="n">
         <v>1</v>
@@ -6897,6 +6897,56 @@
         <v>1260</v>
       </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>codex_new</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.name</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.single</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.many</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>8</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1270</v>
+      </c>
+      <c r="L130" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NotifyType-通知类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:L132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6856,27 +6856,27 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>content_error</t>
+          <t>era_depleted</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>notify.type.content_error.name</t>
+          <t>notify.type.era_depleted.name</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>notify.type.content_error.single</t>
+          <t>notify.type.era_depleted.single</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>notify.type.content_error.many</t>
+          <t>notify.type.era_depleted.many</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -6888,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J129" t="n">
         <v>1</v>
@@ -6906,27 +6906,27 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>codex_new</t>
+          <t>friendly_fire</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.name</t>
+          <t>notify.type.friendly_fire.name</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.single</t>
+          <t>notify.type.friendly_fire.single</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>notify.type.codex_new.many</t>
+          <t>notify.type.friendly_fire.many</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -6938,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J130" t="n">
         <v>1</v>
@@ -6947,6 +6947,106 @@
         <v>1270</v>
       </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>content_error</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.name</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.single</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>notify.type.content_error.many</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>10</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1280</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>codex_new</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.name</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.single</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>notify.type.codex_new.many</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>8</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1290</v>
+      </c>
+      <c r="L132" t="inlineStr">
         <is>
           <t>none</t>
         </is>
